--- a/data/trans_dic/IP24_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,53; 55,74</t>
+          <t>12,57; 30,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 33,33</t>
+          <t>11,64; 30,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 39,39</t>
+          <t>14,14; 26,8</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,6</t>
+          <t>13,35; 21,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 24,23</t>
+          <t>15,58; 22,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 27,93</t>
+          <t>15,27; 20,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 23,1</t>
+          <t>10,95; 20,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 21,54</t>
+          <t>11,63; 21,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,43; 20,18</t>
+          <t>12,66; 19,28</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 34,39</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,48; 20,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 25,82</t>
+          <t>15,47; 19,44</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16888</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>20546</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9587; 30478</t>
+          <t>7009; 16998</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8679; 20357</t>
+          <t>5441; 14056</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21483; 45587</t>
+          <t>14500; 27480</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>129</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>112812</t>
+          <t>78081</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91962</t>
+          <t>79352</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>157433</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85871; 176869</t>
+          <t>63214; 103692</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75371; 124536</t>
+          <t>67058; 94967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169247; 271527</t>
+          <t>138049; 184852</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>25778</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>49452</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18460; 34545</t>
+          <t>18378; 34929</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21715; 39336</t>
+          <t>17446; 31945</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44611; 67025</t>
+          <t>40216; 61273</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>155395</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123419; 227771</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97094; 128435</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>254374; 366625</t>
+          <t>204898; 257387</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que no realizan actividad física en su tiempo libre (o no tienen tiempo libre) (tasa de respuesta: 99,43%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,38%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,57; 30,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11,64; 30,06</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 26,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13,35; 21,89</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15,58; 22,07</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15,27; 20,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,95; 20,82</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11,63; 21,3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12,66; 19,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14,19; 20,76</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15,48; 20,48</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,47; 19,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2059471605849461</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1937701149832725</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2003938185398231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11486</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9060</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20546</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.125668513334756</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1163566282260172</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1414261440828743</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7009; 16998</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5441; 14056</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14500; 27480</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3047831601752276</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3006086933305379</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2680225545511074</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.164836883036323</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.184415405205642</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1741562423437442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>78081</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>79352</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>157433</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1334515975022627</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1558443334221656</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1527134001050408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>63214; 103692</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67058; 94967</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>138049; 184852</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2189061437457295</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2207030501422587</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2044881620075261</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1536469276780344</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1578525013799947</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.15563192993081</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>25778</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>23674</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49452</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1095413603222278</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1163255009994058</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1265656432626134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>18378; 34929</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17446; 31945</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40216; 61273</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2081916205649061</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2130022922756389</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1928329212030047</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1654325638349483</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1787594898776832</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1717427752963914</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>115344</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>112087</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>227431</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1418564869991527</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.154848374123802</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1547269645115697</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>98906; 144738</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>97094; 128435</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>204898; 257387</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2075912977329456</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2048323671866468</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1943637851250347</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no realizan actividad física en su tiempo libre (o no tienen tiempo libre) (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>11486</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9060</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>20546</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>7009</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5441</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>16998</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>14056</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>27480</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>78081</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>79352</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>157433</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>63214</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>67058</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>138049</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>103692</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>94967</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>184852</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>25778</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>23674</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>49452</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>18378</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>17446</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>40216</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>34929</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>31945</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>61273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>186</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>115344</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>112087</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>227431</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>97094</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>204898</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>144738</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>128435</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>257387</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>